--- a/test10.xlsx
+++ b/test10.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jj_on\OneDrive\바탕 화면\ai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jj_on\OneDrive\바탕 화면\hr_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,123 +19,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
-  <x:si>
-    <x:t>국내영업팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김철수</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+  <x:si>
+    <x:t>사원명 (A1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퇴사일 (G1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입사일 (F1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분 (B1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생산2팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부서 (C1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직책 (D1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성별 (E1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영업1팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>품질관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김유유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이철수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최영희</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강건강</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재무팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박지민</x:t>
   </x:si>
   <x:si>
     <x:t>남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직책</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입사일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퇴사일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사원명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김도윤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박소연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김대표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김태형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이준호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정다은</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최민지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재무팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오세훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최지은</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정우성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박민수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강민수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이영희</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한지민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설비팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생산1팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경영지원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해외영업팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>품질관리팀</x:t>
   </x:si>
   <x:si>
     <x:t>공장</x:t>
@@ -145,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -179,19 +137,30 @@
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
+      <x:color rgb="ff1f1f1f"/>
       <x:b val="1"/>
     </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff1f1f1f"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffefefef"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border>
       <x:left>
         <x:color indexed="64"/>
@@ -206,6 +175,20 @@
         <x:color indexed="64"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="ff1f1f1f"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="ff1f1f1f"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="ff1f1f1f"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="ff1f1f1f"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -216,23 +199,13 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -889,348 +862,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G16"/>
+  <x:dimension ref="A1:G6"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.399999999999999"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:7" ht="33.5">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7" ht="17.149999999999999">
+      <x:c r="A2" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="32.75">
-      <x:c r="A2" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F2" s="3">
-        <x:v>45301</x:v>
+        <x:v>45306</x:v>
       </x:c>
       <x:c r="G2" s="2"/>
     </x:row>
-    <x:row r="3" spans="1:7" ht="32.75">
+    <x:row r="3" spans="1:7" ht="17.149999999999999">
       <x:c r="A3" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F3" s="3">
-        <x:v>45000</x:v>
+        <x:v>45056</x:v>
       </x:c>
       <x:c r="G3" s="2"/>
     </x:row>
-    <x:row r="4" spans="1:7" ht="32.75">
+    <x:row r="4" spans="1:7" ht="17.149999999999999">
       <x:c r="A4" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F4" s="3">
-        <x:v>45662</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="G4" s="2"/>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:7" ht="17.149999999999999">
       <x:c r="A5" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F5" s="3">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="G5" s="3">
+        <x:v>46117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7" ht="17.149999999999999">
+      <x:c r="A6" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F5" s="3">
-        <x:v>44824</x:v>
-      </x:c>
-      <x:c r="G5" s="2"/>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="3">
-        <x:v>44327</x:v>
+        <x:v>44788</x:v>
       </x:c>
       <x:c r="G6" s="2"/>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F7" s="3">
-        <x:v>45597</x:v>
-      </x:c>
-      <x:c r="G7" s="2"/>
-    </x:row>
-    <x:row r="8" spans="1:7" ht="32.75">
-      <x:c r="A8" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F8" s="3">
-        <x:v>44742</x:v>
-      </x:c>
-      <x:c r="G8" s="2"/>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E9" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F9" s="3">
-        <x:v>45152</x:v>
-      </x:c>
-      <x:c r="G9" s="2"/>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F10" s="3">
-        <x:v>43466</x:v>
-      </x:c>
-      <x:c r="G10" s="2"/>
-    </x:row>
-    <x:row r="11" spans="1:7" ht="32.75">
-      <x:c r="A11" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="3">
-        <x:v>45698</x:v>
-      </x:c>
-      <x:c r="G11" s="2"/>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F12" s="3">
-        <x:v>45677</x:v>
-      </x:c>
-      <x:c r="G12" s="2"/>
-    </x:row>
-    <x:row r="13" spans="1:7">
-      <x:c r="A13" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E13" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F13" s="3">
-        <x:v>45097</x:v>
-      </x:c>
-      <x:c r="G13" s="2"/>
-    </x:row>
-    <x:row r="14" spans="1:7" ht="32.75">
-      <x:c r="A14" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E14" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F14" s="3">
-        <x:v>44756</x:v>
-      </x:c>
-      <x:c r="G14" s="2"/>
-    </x:row>
-    <x:row r="15" spans="1:7">
-      <x:c r="A15" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E15" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F15" s="3">
-        <x:v>45170</x:v>
-      </x:c>
-      <x:c r="G15" s="2"/>
-    </x:row>
-    <x:row r="16" spans="1:7">
-      <x:c r="A16" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F16" s="3">
-        <x:v>44267</x:v>
-      </x:c>
-      <x:c r="G16" s="3">
-        <x:v>45688</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>

--- a/test10.xlsx
+++ b/test10.xlsx
@@ -21,36 +21,27 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <x:si>
-    <x:t>사원명 (A1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퇴사일 (G1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입사일 (F1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분 (B1)</x:t>
+    <x:t>부서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직책</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
   </x:si>
   <x:si>
     <x:t>생산2팀</x:t>
   </x:si>
   <x:si>
-    <x:t>부서 (C1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직책 (D1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성별 (E1)</x:t>
-  </x:si>
-  <x:si>
     <x:t>영업1팀</x:t>
   </x:si>
   <x:si>
     <x:t>품질관리</x:t>
   </x:si>
   <x:si>
+    <x:t>입사일</x:t>
+  </x:si>
+  <x:si>
     <x:t>김유유</x:t>
   </x:si>
   <x:si>
@@ -97,6 +88,15 @@
   </x:si>
   <x:si>
     <x:t>공장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사원명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퇴사일</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -865,44 +865,44 @@
   <x:dimension ref="A1:G6"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.399999999999999"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="33.5">
+    <x:row r="1" spans="1:7" ht="17.149999999999999">
       <x:c r="A1" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="17.149999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="3">
         <x:v>45306</x:v>
@@ -911,19 +911,19 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="17.149999999999999">
       <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F3" s="3">
         <x:v>45056</x:v>
@@ -932,19 +932,19 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="17.149999999999999">
       <x:c r="A4" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="3">
         <x:v>46101</x:v>
@@ -953,19 +953,19 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="17.149999999999999">
       <x:c r="A5" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="s">
+      <x:c r="C5" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D5" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="3">
         <x:v>45962</x:v>
@@ -976,19 +976,19 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="17.149999999999999">
       <x:c r="A6" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="3">
         <x:v>44788</x:v>
